--- a/output/pdf_financials_xlsx/OR.xlsx
+++ b/output/pdf_financials_xlsx/OR.xlsx
@@ -883,19 +883,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>2.115</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>4.055</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>4.255</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>4.756</v>
@@ -904,19 +904,19 @@
         <v>4.632</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>4.292</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>9.766999999999999</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>5.061</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>4.153</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>4.021</v>
       </c>
     </row>
     <row r="13">
@@ -1594,19 +1594,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-28.558</v>
+        <v>-29.898</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.196</v>
+        <v>-0.919</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>36.722</v>
+        <v>32.667</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>51.578</v>
+        <v>48.318</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-65.935</v>
+        <v>-70.19</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-145.491</v>
@@ -1615,19 +1615,19 @@
         <v>-279.227</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>102.553</v>
+        <v>98.261</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>113.123</v>
+        <v>103.356</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-27.637</v>
+        <v>-32.698</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>30.142</v>
+        <v>25.989</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>241.385</v>
+        <v>237.364</v>
       </c>
     </row>
     <row r="28">
@@ -1680,19 +1680,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-28.558</v>
+        <v>-29.898</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.196</v>
+        <v>-0.919</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>36.722</v>
+        <v>32.667</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>51.578</v>
+        <v>48.318</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-65.935</v>
+        <v>-70.19</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-145.491</v>
@@ -1701,19 +1701,19 @@
         <v>-279.227</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>102.553</v>
+        <v>98.261</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>113.123</v>
+        <v>103.356</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-27.637</v>
+        <v>-32.698</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>30.142</v>
+        <v>25.989</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>241.385</v>
+        <v>237.364</v>
       </c>
     </row>
     <row r="30">
@@ -1728,16 +1728,16 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>6.961988474300017</v>
+        <v>-5.349554688864311</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>80.85874710998569</v>
+        <v>71.92997908180116</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>82.29174976466646</v>
+        <v>77.09047976131596</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-30.92403947170944</v>
+        <v>-32.91966831757467</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-29.66346702767946</v>
@@ -1746,19 +1746,19 @@
         <v>-71.12269771446184</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>45.60404132036624</v>
+        <v>43.69544239739947</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>51.93678865427967</v>
+        <v>47.45258460394199</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-15.08339336782588</v>
+        <v>-17.84552579300107</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>15.76819054494473</v>
+        <v>13.59563081655393</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>87.02635468868299</v>
+        <v>85.57666654649024</v>
       </c>
     </row>
     <row r="31">
@@ -1881,22 +1881,22 @@
         <v>174.265</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>108.223</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>115.698</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>90.548</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>66.85299999999999</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>59.096</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>142.131</v>
       </c>
     </row>
     <row r="35">
@@ -1967,22 +1967,22 @@
         <v>184.265</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>20.704</v>
+        <v>128.927</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>115.698</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>90.548</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>75.053</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>6.2</v>
+        <v>65.29600000000001</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>142.131</v>
       </c>
     </row>
     <row r="37">
@@ -2483,22 +2483,22 @@
         <v>1.015</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>113.395</v>
+        <v>5.172</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>119.639</v>
+        <v>3.941</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>93.09399999999999</v>
+        <v>2.546</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>60.533</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>54.508</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>144.457</v>
+        <v>2.326</v>
       </c>
     </row>
     <row r="49">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -34840,7 +34840,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -42404,7 +42404,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E488" s="5" t="n">

--- a/output/pdf_financials_xlsx/OR.xlsx
+++ b/output/pdf_financials_xlsx/OR.xlsx
@@ -1110,13 +1110,13 @@
         <v>9.724</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>23.147</v>
+        <v>-23.147</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>35.148</v>
+        <v>-35.148</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>40.4</v>
+        <v>-40.4</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>25.926</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-28.432</v>
+        <v>-28.684</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1673.168</v>
+        <v>-2.095</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>28.528</v>
@@ -1339,10 +1339,10 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-133.302</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>-268.475</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-28.432</v>
+        <v>-455.103</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>1673.168</v>
@@ -1431,7 +1431,7 @@
         <v>-183.19</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-48.343</v>
+        <v>-37.426</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>16.267</v>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>43.078788</v>
+        <v>689.55</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>45.966154</v>
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>241.715</v>
+        <v>187.13</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>180.744444</v>
@@ -1840,7 +1840,7 @@
         <v>-84.10579911757549</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>-26.38406793721483</v>
+        <v>-20.42591743619971</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>8.509758993915996</v>
@@ -2124,13 +2124,13 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.491</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>0</v>
@@ -2167,13 +2167,13 @@
         <v>8.416</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.244</v>
+        <v>6.735</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>8.416</v>
+        <v>9.036</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>8.385</v>
@@ -2468,13 +2468,13 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.315</v>
+        <v>0.181</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.508</v>
+        <v>0.017</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.974</v>
+        <v>0.354</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.984</v>
@@ -3177,40 +3177,40 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>33.635</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.721</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.927</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>1.394</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.411</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.217</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>6.836</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.648</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>2.373</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>1.378</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>3.037</v>
       </c>
     </row>
     <row r="65">
@@ -3306,16 +3306,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>28.542</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>1.061</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.652</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.666</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
@@ -3459,16 +3459,16 @@
         <v>0</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.921</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.852</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>1.207</v>
       </c>
     </row>
     <row r="71">
@@ -3502,16 +3502,16 @@
         <v>294.891</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.921</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.852</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>1.207</v>
       </c>
     </row>
     <row r="72">
@@ -3674,16 +3674,16 @@
         <v>21.336</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>11.042</v>
+        <v>10.121</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>8.151999999999999</v>
+        <v>7.472</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>9.285</v>
+        <v>8.433</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>25.155</v>
+        <v>23.948</v>
       </c>
     </row>
     <row r="76">
@@ -3893,16 +3893,16 @@
         <v>0.2305735589960119</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.08902257699266238</v>
+        <v>0.08955273711713775</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.08902144938293359</v>
+        <v>0.08955162205549505</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.08228331986209715</v>
+        <v>0.08299991673346213</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.00265006379007305</v>
+        <v>0.00349291675308179</v>
       </c>
     </row>
     <row r="81">
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>-28.432</v>
+        <v>-28.684</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>1673.168</v>
+        <v>-2.095</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>28.528</v>
@@ -4677,7 +4677,7 @@
         <v>-183.19</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>-48.343</v>
+        <v>-37.426</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>16.267</v>
@@ -5295,40 +5295,40 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-0.019</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-30.681</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-171.54</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-82.384</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-226.766</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-104.746</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-62.815</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-7.416</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0</v>
+        <v>-0.048</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-40.2</v>
       </c>
       <c r="L114" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>0</v>
+        <v>-12.599</v>
       </c>
     </row>
     <row r="115">
@@ -5359,19 +5359,19 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>7.882</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>98.053</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>3.847</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>49.805</v>
       </c>
     </row>
     <row r="116">
@@ -5700,22 +5700,22 @@
         <v>0</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>0</v>
+        <v>19.772</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>0</v>
+        <v>147.833</v>
       </c>
       <c r="K123" s="3" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="L123" s="3" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>0</v>
+        <v>10.437</v>
       </c>
     </row>
     <row r="124">
@@ -5786,22 +5786,22 @@
         <v>-123.475</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>-30</v>
+        <v>-10.228</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>-413.12</v>
+        <v>-265.287</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>-155.787</v>
+        <v>34.213</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>-84.721</v>
+        <v>-49.721</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>-105.372</v>
+        <v>-94.935</v>
       </c>
     </row>
     <row r="126">
@@ -7344,7 +7344,11 @@
           <t>Lease liabilities 14</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -8942,7 +8946,11 @@
           <t>Lease liabilities 15 852</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -10308,7 +10316,11 @@
           <t>Lease liabilities 15</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -19508,7 +19520,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E179" s="5" t="n">
         <v>0.126</v>
       </c>
@@ -19896,7 +19912,11 @@
           <t>Acquisitions of investments</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -19966,7 +19986,11 @@
           <t>Proceeds from disposal of investments 10</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -20332,7 +20356,11 @@
           <t>Increase in long-term debt 15</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -21926,7 +21954,11 @@
           <t>Proceeds from disposal of investments 10, 11</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -22132,7 +22164,11 @@
           <t>Increase in long-term debt 16</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -22930,7 +22966,11 @@
           <t>Net gain on acquisition of investments</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -25072,7 +25112,11 @@
           <t>Proceeds from disposal of investments</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -25454,7 +25498,11 @@
           <t>Increase in long-term debt 17</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -26352,7 +26400,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -26870,7 +26922,11 @@
           <t>Acquisition of investments</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -27296,7 +27352,11 @@
           <t>Increase in long-term debt</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -27902,7 +27962,11 @@
           <t>Net (gain) loss on acquisition of investments</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -29440,7 +29504,11 @@
           <t>Net loss (gain) on acquisition of investments</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -29514,7 +29582,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -30262,7 +30334,11 @@
           <t>Loss (gain) on acquisition of investments</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
@@ -32886,7 +32962,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E361" s="5" t="n">
         <v>-28.684</v>
       </c>
@@ -33334,7 +33414,11 @@
           <t>Acquisition of investments</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E367" s="5" t="n">
         <v>-0.019</v>
       </c>
@@ -36468,7 +36552,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -37158,7 +37246,11 @@
           <t>Net loss from discontinued operations 29</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -38348,7 +38440,11 @@
           <t>Net loss from discontinued operations 31</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
           <t>-</t>
@@ -39546,7 +39642,11 @@
           <t>Income tax recovery 24</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
@@ -40380,7 +40480,11 @@
           <t>Income tax recovery 23</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E461" t="inlineStr">
         <is>
           <t>-</t>
@@ -41434,7 +41538,11 @@
           <t>Income tax recovery (expense) 25</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E475" t="inlineStr">
         <is>
           <t>-</t>
@@ -45286,7 +45394,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D526" t="inlineStr"/>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E526" s="5" t="n">
         <v>-28.684</v>
       </c>
@@ -45434,7 +45546,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D528" t="inlineStr"/>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E528" s="5" t="n">
         <v>-455.103</v>
       </c>
